--- a/Config/MiniTemplate/Datas/language.xlsx
+++ b/Config/MiniTemplate/Datas/language.xlsx
@@ -37,10 +37,10 @@
     <t>id</t>
   </si>
   <si>
-    <t>Chinese</t>
-  </si>
-  <si>
-    <t>ChineseTW</t>
+    <t>ChineseSimplified</t>
+  </si>
+  <si>
+    <t>ChineseTraditional</t>
   </si>
   <si>
     <t>English</t>
